--- a/data/trans_orig/P04B3_2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9784</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23026</t>
+          <t>21925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42324</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>34944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27929</t>
+          <t>27685</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32746</t>
+          <t>32814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55183</t>
+          <t>57429</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>256622</t>
+          <t>257625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281948</t>
+          <t>282573</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>241628</t>
+          <t>241827</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259206</t>
+          <t>258888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>506896</t>
+          <t>503515</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>536089</t>
+          <t>536825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>23170</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32274</t>
+          <t>34227</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32235</t>
+          <t>34028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>70752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38868</t>
+          <t>38960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62034</t>
+          <t>62109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79148</t>
+          <t>78164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121570</t>
+          <t>118305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177288</t>
+          <t>178282</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>236592</t>
+          <t>236612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162331</t>
+          <t>161984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202025</t>
+          <t>202452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355154</t>
+          <t>354196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>422777</t>
+          <t>425876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>225489</t>
+          <t>225404</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>282682</t>
+          <t>285512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>253791</t>
+          <t>253462</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>295451</t>
+          <t>295404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>495441</t>
+          <t>497127</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>564423</t>
+          <t>568394</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48708</t>
+          <t>47900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24515</t>
+          <t>24069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43075</t>
+          <t>42065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55233</t>
+          <t>55775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84739</t>
+          <t>82757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49664</t>
+          <t>49734</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46488</t>
+          <t>46153</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>69575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>79887</t>
+          <t>79714</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>111777</t>
+          <t>112326</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44937</t>
+          <t>44422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73071</t>
+          <t>70753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34696</t>
+          <t>35381</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55797</t>
+          <t>55392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86079</t>
+          <t>84813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118851</t>
+          <t>121278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167310</t>
+          <t>167825</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204396</t>
+          <t>202355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201519</t>
+          <t>200054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>231584</t>
+          <t>229766</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>379120</t>
+          <t>375836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424125</t>
+          <t>422828</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>37726</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31704</t>
+          <t>32447</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>246422</t>
+          <t>245724</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52645</t>
+          <t>52482</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>316627</t>
+          <t>304594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33969</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>62102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65241</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66615</t>
+          <t>66482</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115511</t>
+          <t>116167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46840</t>
+          <t>46766</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78875</t>
+          <t>79894</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37967</t>
+          <t>39803</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85354</t>
+          <t>86225</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>93272</t>
+          <t>88519</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155325</t>
+          <t>152391</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>163026</t>
+          <t>158749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204172</t>
+          <t>203728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169476</t>
+          <t>165274</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>320848</t>
+          <t>320383</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>323223</t>
+          <t>331339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>507614</t>
+          <t>507820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>35449</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57463</t>
+          <t>57089</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45595</t>
+          <t>46329</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>54935</t>
+          <t>56859</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95710</t>
+          <t>97985</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11662</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>452</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>116096</t>
+          <t>115945</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>137451</t>
+          <t>138108</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>199529</t>
+          <t>200138</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>234145</t>
+          <t>234922</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324211</t>
+          <t>322594</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>372261</t>
+          <t>370228</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29309</t>
+          <t>29986</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51173</t>
+          <t>50434</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>40216</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58453</t>
+          <t>58863</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84289</t>
+          <t>85802</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39301</t>
+          <t>40333</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>43648</t>
+          <t>44645</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>52490</t>
+          <t>50602</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>77318</t>
+          <t>76947</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>46090</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45180</t>
+          <t>45247</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>58387</t>
+          <t>57864</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>85186</t>
+          <t>85219</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>152354</t>
+          <t>151832</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>180719</t>
+          <t>180015</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>141799</t>
+          <t>143974</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>166110</t>
+          <t>168929</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>302754</t>
+          <t>302269</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>340302</t>
+          <t>342032</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30801</t>
+          <t>32074</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>57019</t>
+          <t>57539</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>26307</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>87573</t>
+          <t>86930</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>66328</t>
+          <t>65354</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>130108</t>
+          <t>131979</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>81428</t>
+          <t>82280</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>122954</t>
+          <t>124674</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>47678</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>138183</t>
+          <t>138324</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>132334</t>
+          <t>130377</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>240996</t>
+          <t>244763</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>132039</t>
+          <t>132206</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>182567</t>
+          <t>183871</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>74523</t>
+          <t>79714</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>232351</t>
+          <t>232622</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>206694</t>
+          <t>200036</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>390386</t>
+          <t>390976</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>295733</t>
+          <t>295305</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>353216</t>
+          <t>355501</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>397914</t>
+          <t>400424</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>702004</t>
+          <t>694232</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>724578</t>
+          <t>723664</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1043711</t>
+          <t>1070139</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>179920</t>
+          <t>172160</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>548413</t>
+          <t>549058</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>401471</t>
+          <t>400463</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>446503</t>
+          <t>444504</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>508133</t>
+          <t>507556</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>971717</t>
+          <t>972772</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>68160</t>
+          <t>67106</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>222985</t>
+          <t>224264</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>139693</t>
+          <t>142221</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>178276</t>
+          <t>177348</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>199510</t>
+          <t>193571</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>384779</t>
+          <t>384493</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>36106</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>127513</t>
+          <t>128658</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>77568</t>
+          <t>76305</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>107745</t>
+          <t>105183</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>107918</t>
+          <t>110034</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>219455</t>
+          <t>219232</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>51959</t>
+          <t>51625</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>646231</t>
+          <t>644676</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>34991</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>57633</t>
+          <t>56278</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>96074</t>
+          <t>96450</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>830318</t>
+          <t>824768</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>465601</t>
+          <t>446506</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>657962</t>
+          <t>654071</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>592220</t>
+          <t>598131</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>866976</t>
+          <t>878198</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1136772</t>
+          <t>1141418</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1481489</t>
+          <t>1479373</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>352507</t>
+          <t>345707</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>492777</t>
+          <t>492840</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>377338</t>
+          <t>375100</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>512781</t>
+          <t>511177</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,47 +5445,47 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>906202</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>781012</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>990492</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
           <t>13,82%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>906202</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>786088</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>985818</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>484051</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>699783</t>
+          <t>698913</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>493712</t>
+          <t>490102</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>675052</t>
+          <t>673658</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1085969</t>
+          <t>1064088</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1350896</t>
+          <t>1345885</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1645153</t>
+          <t>1651354</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2142814</t>
+          <t>2185610</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1786584</t>
+          <t>1789669</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2244576</t>
+          <t>2263394</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3501702</t>
+          <t>3475101</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4196237</t>
+          <t>4185219</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>25766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>18960</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>29021</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31058</t>
+          <t>36467</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>26551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22448</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>45394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>43428</t>
+          <t>63728</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32814</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57429</t>
+          <t>80959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>271257</t>
+          <t>266601</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>257625</t>
+          <t>252598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>282573</t>
+          <t>278717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,67 +1099,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>251050</t>
+          <t>263476</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>241827</t>
+          <t>249526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>258888</t>
+          <t>273607</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>78,95%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>86,57%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>530077</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>510776</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>546402</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>83,49%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>89,38%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>728</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>522306</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>503515</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>536825</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>86,89%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23170</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34227</t>
+          <t>32711</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48107</t>
+          <t>49109</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34028</t>
+          <t>34024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70752</t>
+          <t>66287</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>49752</t>
+          <t>53098</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38960</t>
+          <t>41904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62109</t>
+          <t>67393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97859</t>
+          <t>102207</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78164</t>
+          <t>82909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118305</t>
+          <t>125405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>206625</t>
+          <t>213680</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178282</t>
+          <t>187946</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>236612</t>
+          <t>243254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180881</t>
+          <t>194683</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161984</t>
+          <t>174642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202452</t>
+          <t>215374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>387506</t>
+          <t>408363</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>354196</t>
+          <t>373861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>425876</t>
+          <t>448644</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>255167</t>
+          <t>259920</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>225404</t>
+          <t>230256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285512</t>
+          <t>288441</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>274424</t>
+          <t>288755</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>253462</t>
+          <t>267380</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>295404</t>
+          <t>309119</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>529590</t>
+          <t>548675</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>497127</t>
+          <t>510130</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>568394</t>
+          <t>583879</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36006</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>28074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47900</t>
+          <t>50148</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>34767</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24069</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>44753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>68613</t>
+          <t>72985</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55775</t>
+          <t>60180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82757</t>
+          <t>87924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37741</t>
+          <t>38288</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>28349</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49734</t>
+          <t>48853</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57025</t>
+          <t>60035</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46153</t>
+          <t>47632</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69575</t>
+          <t>72328</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>94767</t>
+          <t>98323</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>79714</t>
+          <t>83447</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112326</t>
+          <t>116160</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>56283</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44422</t>
+          <t>44296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70753</t>
+          <t>69936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44019</t>
+          <t>46205</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35381</t>
+          <t>36357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55392</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>101024</t>
+          <t>102488</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84813</t>
+          <t>87732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121278</t>
+          <t>121079</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>185298</t>
+          <t>183204</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167825</t>
+          <t>167009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202355</t>
+          <t>200049</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>215477</t>
+          <t>215374</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200054</t>
+          <t>199022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>229766</t>
+          <t>231464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>400775</t>
+          <t>398578</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375836</t>
+          <t>373667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422828</t>
+          <t>421083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37726</t>
+          <t>41987</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>100048</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>245724</t>
+          <t>51064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>122157</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52482</t>
+          <t>48284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>304594</t>
+          <t>84102</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46270</t>
+          <t>51742</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33010</t>
+          <t>36549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62102</t>
+          <t>68318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>52451</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>41339</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>67677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>92257</t>
+          <t>104193</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66482</t>
+          <t>84809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116167</t>
+          <t>127967</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61725</t>
+          <t>67831</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46766</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>79894</t>
+          <t>88943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64515</t>
+          <t>72817</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>59592</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86225</t>
+          <t>86013</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>140648</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88519</t>
+          <t>120693</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>152391</t>
+          <t>167194</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>182453</t>
+          <t>228578</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158749</t>
+          <t>201018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203728</t>
+          <t>251310</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>265006</t>
+          <t>257358</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165274</t>
+          <t>237477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>320383</t>
+          <t>275049</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>447459</t>
+          <t>485936</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>331339</t>
+          <t>454806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>507820</t>
+          <t>514730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475556</t>
+          <t>420993</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788113</t>
+          <t>794138</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45878</t>
+          <t>55887</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35449</t>
+          <t>46121</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57089</t>
+          <t>69479</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>31818</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46329</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>79666</t>
+          <t>95451</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>81208</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97985</t>
+          <t>110850</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>127629</t>
+          <t>142767</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>115945</t>
+          <t>128983</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>138108</t>
+          <t>153338</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>214435</t>
+          <t>178822</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>200138</t>
+          <t>168450</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>234922</t>
+          <t>187163</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>342065</t>
+          <t>321588</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>322594</t>
+          <t>304994</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>370228</t>
+          <t>336556</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29986</t>
+          <t>33323</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50434</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>31044</t>
+          <t>33445</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23225</t>
+          <t>25851</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40216</t>
+          <t>43449</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>70428</t>
+          <t>76256</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58863</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85802</t>
+          <t>90454</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>30557</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>40858</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34704</t>
+          <t>36914</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44645</t>
+          <t>46343</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>63625</t>
+          <t>67471</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50602</t>
+          <t>56314</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>76947</t>
+          <t>80879</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>35022</t>
+          <t>34425</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26486</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46090</t>
+          <t>43905</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>35671</t>
+          <t>36137</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27210</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45247</t>
+          <t>45396</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>70562</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>57864</t>
+          <t>57723</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>85219</t>
+          <t>83930</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>166310</t>
+          <t>162914</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>151832</t>
+          <t>149425</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>180015</t>
+          <t>176527</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>155636</t>
+          <t>157255</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>143974</t>
+          <t>144939</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>168929</t>
+          <t>170822</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>321946</t>
+          <t>320169</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>302269</t>
+          <t>301042</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>342032</t>
+          <t>338644</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>43216</t>
+          <t>51184</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>57539</t>
+          <t>68419</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>62278</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>26307</t>
+          <t>63295</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>86930</t>
+          <t>93997</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>105494</t>
+          <t>129215</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>65354</t>
+          <t>109195</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>131979</t>
+          <t>148860</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>100541</t>
+          <t>115294</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>82280</t>
+          <t>92911</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>124674</t>
+          <t>137368</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>100067</t>
+          <t>123499</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>47678</t>
+          <t>106101</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>138324</t>
+          <t>144896</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>200608</t>
+          <t>238793</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>130377</t>
+          <t>209458</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>244763</t>
+          <t>268847</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>155298</t>
+          <t>174467</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>132206</t>
+          <t>147914</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>183871</t>
+          <t>200630</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>169750</t>
+          <t>203794</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>79714</t>
+          <t>183315</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>232622</t>
+          <t>229166</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>325048</t>
+          <t>378261</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>200036</t>
+          <t>344705</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>390976</t>
+          <t>414730</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>324895</t>
+          <t>375922</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>295305</t>
+          <t>348921</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>355501</t>
+          <t>409965</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>514358</t>
+          <t>363189</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>400424</t>
+          <t>335206</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>694232</t>
+          <t>386379</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>839253</t>
+          <t>739111</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>723664</t>
+          <t>696501</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1070139</t>
+          <t>777584</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623950</t>
+          <t>716866</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623950</t>
+          <t>716866</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623950</t>
+          <t>716866</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>846453</t>
+          <t>768513</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>846453</t>
+          <t>768513</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>846453</t>
+          <t>768513</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1470403</t>
+          <t>1485380</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1470403</t>
+          <t>1485380</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1470403</t>
+          <t>1485380</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>395225</t>
+          <t>466701</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>172160</t>
+          <t>437678</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>549058</t>
+          <t>496717</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>423303</t>
+          <t>490203</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>400463</t>
+          <t>463099</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>444504</t>
+          <t>516345</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>818529</t>
+          <t>956904</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>507556</t>
+          <t>916792</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>972772</t>
+          <t>993507</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>158824</t>
+          <t>181445</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>67106</t>
+          <t>157136</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>224264</t>
+          <t>208769</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>158290</t>
+          <t>178755</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>142221</t>
+          <t>159283</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>177348</t>
+          <t>201284</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>317115</t>
+          <t>360201</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>193571</t>
+          <t>327828</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>384493</t>
+          <t>393529</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>88449</t>
+          <t>101523</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>36106</t>
+          <t>82295</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>128658</t>
+          <t>120495</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>91319</t>
+          <t>106421</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>76305</t>
+          <t>90026</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>105183</t>
+          <t>122420</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>179768</t>
+          <t>207943</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>110034</t>
+          <t>181437</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>219232</t>
+          <t>234551</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>286222</t>
+          <t>48403</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>36086</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>644676</t>
+          <t>65671</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>44660</t>
+          <t>54976</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>42999</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>56278</t>
+          <t>68988</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>330882</t>
+          <t>103380</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>96450</t>
+          <t>83953</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>824768</t>
+          <t>125160</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717572</t>
+          <t>830356</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717572</t>
+          <t>830356</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717572</t>
+          <t>830356</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1646293</t>
+          <t>1628428</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1646293</t>
+          <t>1628428</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1646293</t>
+          <t>1628428</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>592007</t>
+          <t>689718</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>446506</t>
+          <t>641930</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>654071</t>
+          <t>741806</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>695567</t>
+          <t>726985</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>598131</t>
+          <t>688236</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>878198</t>
+          <t>773570</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1287574</t>
+          <t>1416703</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1141418</t>
+          <t>1354131</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1479373</t>
+          <t>1485203</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>440088</t>
+          <t>489252</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>345707</t>
+          <t>444064</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>492840</t>
+          <t>530529</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>466114</t>
+          <t>529865</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>375100</t>
+          <t>492351</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>511177</t>
+          <t>567830</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>906202</t>
+          <t>1019117</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>781012</t>
+          <t>962535</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>990492</t>
+          <t>1077239</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>628162</t>
+          <t>682661</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>484051</t>
+          <t>629727</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>698913</t>
+          <t>737750</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>612421</t>
+          <t>695413</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>490102</t>
+          <t>653627</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>673658</t>
+          <t>736934</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1240583</t>
+          <t>1378074</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1064088</t>
+          <t>1314409</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1345885</t>
+          <t>1448793</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1799231</t>
+          <t>1668310</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1651354</t>
+          <t>1604490</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2185610</t>
+          <t>1740686</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1935045</t>
+          <t>1779205</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1789669</t>
+          <t>1721265</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2263394</t>
+          <t>1830214</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3734276</t>
+          <t>3447514</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3475101</t>
+          <t>3371320</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4185219</t>
+          <t>3530460</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3459488</t>
+          <t>3529941</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3459488</t>
+          <t>3529941</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3459488</t>
+          <t>3529941</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3709148</t>
+          <t>3731467</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3709148</t>
+          <t>3731467</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3709148</t>
+          <t>3731467</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7168635</t>
+          <t>7261408</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7168635</t>
+          <t>7261408</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7168635</t>
+          <t>7261408</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
